--- a/diseases/d233/2015-2019.xlsx
+++ b/diseases/d233/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN121" t="b">

--- a/diseases/d233/2015-2019.xlsx
+++ b/diseases/d233/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
